--- a/artfynd/A 43609-2023 artfynd.xlsx
+++ b/artfynd/A 43609-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43609-2023 artfynd.xlsx
+++ b/artfynd/A 43609-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56442470</v>
+        <v>69500807</v>
       </c>
       <c r="B2" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>720</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659838.2077449972</v>
+        <v>659900</v>
       </c>
       <c r="R2" t="n">
-        <v>6716154.458527082</v>
+        <v>6716277</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +748,14 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 m lång sträng vid en gammal rotvälta, i äldre barrskog.</t>
+          <t>Ca. 10 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69500807</v>
+        <v>69500808</v>
       </c>
       <c r="B3" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,17 +807,13 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659899.8534231293</v>
+        <v>659912</v>
       </c>
       <c r="R3" t="n">
-        <v>6716277.375613662</v>
+        <v>6716100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,24 +860,14 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca. 10 ex. i äldre, fuktig barrskog.</t>
+          <t>3 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +902,7 @@
         <v>69500809</v>
       </c>
       <c r="B4" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,14 +919,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>11</t>
@@ -977,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659890.2947033279</v>
+        <v>659890</v>
       </c>
       <c r="R4" t="n">
-        <v>6716237.055141035</v>
+        <v>6716237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,19 +972,9 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1062,12 +1014,7 @@
         <v>69500810</v>
       </c>
       <c r="B5" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,14 +1031,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
@@ -1108,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659934.4886421458</v>
+        <v>659934</v>
       </c>
       <c r="R5" t="n">
-        <v>6716308.46475082</v>
+        <v>6716308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,19 +1084,9 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1190,42 +1123,33 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69506530</v>
+        <v>69500811</v>
       </c>
       <c r="B6" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>473</v>
+        <v>433</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Bon</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1239,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659852.4129191471</v>
+        <v>659892</v>
       </c>
       <c r="R6" t="n">
-        <v>6716167.894970816</v>
+        <v>6716098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,24 +1196,14 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3 ex. i äldre barrskog.</t>
+          <t>1 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,7 +1217,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1321,42 +1235,33 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69510780</v>
+        <v>112092635</v>
       </c>
       <c r="B7" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1364,16 +1269,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
+          <t>Truskesjön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659895.4365990878</v>
+        <v>659899</v>
       </c>
       <c r="R7" t="n">
-        <v>6716232.35767484</v>
+        <v>6716085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1400,27 +1307,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca. 5 ex. i äldre, fuktig barrskog.</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,38 +1321,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre, fuktig barrskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>69506525</v>
       </c>
       <c r="B8" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659955.594998274</v>
+        <v>659956</v>
       </c>
       <c r="R8" t="n">
-        <v>6716233.056210049</v>
+        <v>6716233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,19 +1421,9 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1583,15 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69506529</v>
+        <v>69506526</v>
       </c>
       <c r="B9" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659885.3926458675</v>
+        <v>659952</v>
       </c>
       <c r="R9" t="n">
-        <v>6716236.345174636</v>
+        <v>6716133</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,24 +1537,14 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>3 ex. i äldre, fuktig barrskog.</t>
+          <t>3 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1696,7 +1558,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre, fuktig barrskog.</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1714,42 +1576,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69510777</v>
+        <v>69506527</v>
       </c>
       <c r="B10" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>473</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1763,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659951.7082155341</v>
+        <v>659905</v>
       </c>
       <c r="R10" t="n">
-        <v>6716142.745338813</v>
+        <v>6716277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1796,24 +1653,14 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca. 5 ex. i äldre barrskog.</t>
+          <t>1 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1827,7 +1674,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1848,12 +1695,7 @@
         <v>69506528</v>
       </c>
       <c r="B11" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1894,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659891.7555049127</v>
+        <v>659892</v>
       </c>
       <c r="R11" t="n">
-        <v>6716204.118789022</v>
+        <v>6716204</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1927,19 +1769,9 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1976,42 +1808,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>69510779</v>
+        <v>69506529</v>
       </c>
       <c r="B12" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>473</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2025,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>659899.9097161937</v>
+        <v>659885</v>
       </c>
       <c r="R12" t="n">
-        <v>6716287.229032927</v>
+        <v>6716236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2058,24 +1885,14 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca. 5 ex. i äldre, fuktig barrskog.</t>
+          <t>3 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2107,42 +1924,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69507129</v>
+        <v>69506530</v>
       </c>
       <c r="B13" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>473</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2156,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>659856.1994945928</v>
+        <v>659852</v>
       </c>
       <c r="R13" t="n">
-        <v>6716171.51079747</v>
+        <v>6716168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,24 +2001,14 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ca. 5 ex. i äldre barrskog.</t>
+          <t>3 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2238,15 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69506526</v>
+        <v>112092582</v>
       </c>
       <c r="B14" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2271,26 +2068,20 @@
           <t>Bon</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
+          <t>Truskesjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>659951.6520383013</v>
+        <v>659984</v>
       </c>
       <c r="R14" t="n">
-        <v>6716132.891517933</v>
+        <v>6716134</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2317,27 +2108,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>3 ex. i äldre barrskog.</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2346,82 +2122,68 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre barrskog.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>69510781</v>
+        <v>56442470</v>
       </c>
       <c r="B15" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3762</v>
+        <v>720</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>659851.197302529</v>
+        <v>659838</v>
       </c>
       <c r="R15" t="n">
-        <v>6716161.930333578</v>
+        <v>6716154</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2451,24 +2213,14 @@
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2005-09-19</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ca. 5 ex. i äldre barrskog.</t>
+          <t>1 m lång sträng vid en gammal rotvälta, i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2500,42 +2252,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>69506527</v>
+        <v>112092533</v>
       </c>
       <c r="B16" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>473</v>
+        <v>720</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2543,16 +2290,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
+          <t>Truskesjön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>659904.7990327543</v>
+        <v>659887</v>
       </c>
       <c r="R16" t="n">
-        <v>6716277.102435823</v>
+        <v>6716187</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2579,27 +2328,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 ex. i äldre, fuktig barrskog.</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2608,73 +2342,68 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre, fuktig barrskog.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>75873399</v>
+        <v>112834230</v>
       </c>
       <c r="B17" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>720</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
+          <t>Truskesjön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>659841.694145509</v>
+        <v>659886</v>
       </c>
       <c r="R17" t="n">
-        <v>6716131.462587531</v>
+        <v>6716188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,27 +2430,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2005-09-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2736,53 +2450,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Elin Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elin Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112092566</v>
+        <v>112092501</v>
       </c>
       <c r="B18" t="n">
-        <v>90698</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>789</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2791,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>659952</v>
+        <v>659896</v>
       </c>
       <c r="R18" t="n">
-        <v>6716156</v>
+        <v>6716298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2827,6 +2548,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer intill blek fingersvamp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2858,15 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112092516</v>
+        <v>75873399</v>
       </c>
       <c r="B19" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2874,37 +2595,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>659895</v>
+        <v>659842</v>
       </c>
       <c r="R19" t="n">
-        <v>6716298</v>
+        <v>6716131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2931,12 +2649,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2945,60 +2668,50 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112092582</v>
+        <v>112092514</v>
       </c>
       <c r="B20" t="n">
-        <v>85579</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>473</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3011,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>659985</v>
+        <v>659896</v>
       </c>
       <c r="R20" t="n">
-        <v>6716134</v>
+        <v>6716298</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3078,15 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112092669</v>
+        <v>112092565</v>
       </c>
       <c r="B21" t="n">
-        <v>89549</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3121,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>659824</v>
+        <v>659951</v>
       </c>
       <c r="R21" t="n">
-        <v>6716121</v>
+        <v>6716156</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3188,37 +2896,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112092465</v>
+        <v>112092669</v>
       </c>
       <c r="B22" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>3215</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3231,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659975</v>
+        <v>659824</v>
       </c>
       <c r="R22" t="n">
-        <v>6716342</v>
+        <v>6716122</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3298,15 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112092492</v>
+        <v>56381240</v>
       </c>
       <c r="B23" t="n">
-        <v>89316</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,26 +3012,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256756</v>
+        <v>3286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3341,18 +3039,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659895</v>
+        <v>659856</v>
       </c>
       <c r="R23" t="n">
-        <v>6716298</v>
+        <v>6716076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3379,17 +3075,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Växer bredvid raggtaggsvamp</t>
+          <t>4 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3398,38 +3094,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112092482</v>
+        <v>69507129</v>
       </c>
       <c r="B24" t="n">
-        <v>90698</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3437,37 +3128,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>659967</v>
+        <v>659856</v>
       </c>
       <c r="R24" t="n">
-        <v>6716303</v>
+        <v>6716172</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3494,12 +3191,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3508,72 +3210,59 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112092533</v>
+        <v>112092471</v>
       </c>
       <c r="B25" t="n">
-        <v>89275</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>720</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3582,10 +3271,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659887</v>
+        <v>659958</v>
       </c>
       <c r="R25" t="n">
-        <v>6716187</v>
+        <v>6716383</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3649,15 +3338,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112092514</v>
+        <v>112092477</v>
       </c>
       <c r="B26" t="n">
-        <v>89549</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3665,21 +3349,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3692,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>659895</v>
+        <v>659967</v>
       </c>
       <c r="R26" t="n">
-        <v>6716298</v>
+        <v>6716303</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3759,15 +3443,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112092668</v>
+        <v>112092516</v>
       </c>
       <c r="B27" t="n">
-        <v>91053</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3775,21 +3454,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>659824</v>
+        <v>659896</v>
       </c>
       <c r="R27" t="n">
-        <v>6716121</v>
+        <v>6716298</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3869,15 +3548,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112092565</v>
+        <v>112092583</v>
       </c>
       <c r="B28" t="n">
-        <v>89549</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3885,21 +3559,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3912,10 +3586,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>659952</v>
+        <v>659984</v>
       </c>
       <c r="R28" t="n">
-        <v>6716156</v>
+        <v>6716134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3979,49 +3653,36 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112092501</v>
+        <v>112092666</v>
       </c>
       <c r="B29" t="n">
-        <v>91615</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>789</v>
+        <v>3674</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -4030,10 +3691,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>659896</v>
+        <v>659824</v>
       </c>
       <c r="R29" t="n">
-        <v>6716298</v>
+        <v>6716122</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4066,11 +3727,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växer intill blek fingersvamp</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4102,15 +3758,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112092455</v>
+        <v>69510777</v>
       </c>
       <c r="B30" t="n">
-        <v>90698</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4118,37 +3769,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>659994</v>
+        <v>659952</v>
       </c>
       <c r="R30" t="n">
-        <v>6716342</v>
+        <v>6716143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4175,12 +3832,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4189,76 +3851,77 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112092449</v>
+        <v>69510778</v>
       </c>
       <c r="B31" t="n">
-        <v>85635</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>659994</v>
+        <v>659908</v>
       </c>
       <c r="R31" t="n">
-        <v>6716342</v>
+        <v>6716099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4285,12 +3948,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4299,38 +3967,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre, fuktig barrskog.</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112092471</v>
+        <v>69510779</v>
       </c>
       <c r="B32" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4338,37 +4001,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659958</v>
+        <v>659900</v>
       </c>
       <c r="R32" t="n">
-        <v>6716383</v>
+        <v>6716287</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4395,12 +4064,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4409,38 +4083,33 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre, fuktig barrskog.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112092553</v>
+        <v>69510780</v>
       </c>
       <c r="B33" t="n">
-        <v>91044</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,37 +4117,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>659887</v>
+        <v>659895</v>
       </c>
       <c r="R33" t="n">
-        <v>6716187</v>
+        <v>6716232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4505,12 +4180,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. i äldre, fuktig barrskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4519,76 +4199,77 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Äldre, fuktig barrskog.</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112092562</v>
+        <v>69510781</v>
       </c>
       <c r="B34" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>3762</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659952</v>
+        <v>659851</v>
       </c>
       <c r="R34" t="n">
-        <v>6716156</v>
+        <v>6716162</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4615,12 +4296,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4629,76 +4315,77 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112092521</v>
+        <v>69510782</v>
       </c>
       <c r="B35" t="n">
-        <v>91076</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>3762</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Truskesjön, Upl</t>
+          <t>Truskesjön 2,5 km NO om Hållnäs kyrka, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>659990</v>
+        <v>659823</v>
       </c>
       <c r="R35" t="n">
-        <v>6716251</v>
+        <v>6716073</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4725,12 +4412,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2005-09-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex. i äldre barrskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4739,60 +4431,55 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112092666</v>
+        <v>112092553</v>
       </c>
       <c r="B36" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3674</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4805,10 +4492,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>659824</v>
+        <v>659887</v>
       </c>
       <c r="R36" t="n">
-        <v>6716121</v>
+        <v>6716187</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4872,15 +4559,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112092583</v>
+        <v>112092455</v>
       </c>
       <c r="B37" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4888,21 +4570,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4915,10 +4597,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>659985</v>
+        <v>659994</v>
       </c>
       <c r="R37" t="n">
-        <v>6716134</v>
+        <v>6716341</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4982,15 +4664,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112092477</v>
+        <v>112092482</v>
       </c>
       <c r="B38" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4998,21 +4675,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5092,50 +4769,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112834230</v>
+        <v>112092566</v>
       </c>
       <c r="B39" t="n">
-        <v>89446</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>720</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Truskesjön, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659886</v>
+        <v>659951</v>
       </c>
       <c r="R39" t="n">
-        <v>6716188</v>
+        <v>6716156</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5162,12 +4837,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5176,23 +4851,572 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Larsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Larsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>112092639</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Truskesjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>659899</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6716085</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112092668</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Truskesjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>659824</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6716122</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112092492</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Truskesjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>659896</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6716298</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Växer bredvid raggtaggsvamp</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112092449</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Truskesjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>659994</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6716341</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>112092630</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Truskesjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>659899</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6716085</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 43609-2023 artfynd.xlsx
+++ b/artfynd/A 43609-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69500807</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69500808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69500809</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69500811</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092635</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506527</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506528</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506529</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1693,6 +1738,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506530</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,6 +1850,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442470</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1913,6 +1968,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092533</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2014,6 +2074,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112834230</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2132,6 +2197,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092501</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2234,6 +2304,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75873399</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2339,6 +2414,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092514</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2444,6 +2524,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092669</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2560,6 +2645,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56381240</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2676,6 +2766,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69507129</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092516</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2886,6 +2986,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092666</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3002,6 +3107,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510778</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3118,6 +3228,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510779</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3234,6 +3349,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510780</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3350,6 +3470,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510781</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3466,6 +3591,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510782</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3571,6 +3701,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092553</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3676,6 +3811,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092639</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3781,6 +3921,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092668</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3897,6 +4042,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092492</t>
         </is>
       </c>
     </row>
@@ -4014,6 +4164,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092630</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4126,6 +4281,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69500810</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4242,6 +4402,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506525</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4358,6 +4523,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506526</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4463,6 +4633,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092582</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4568,6 +4743,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092565</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4673,6 +4853,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092471</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4778,6 +4963,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092477</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4883,6 +5073,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092583</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4999,6 +5194,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510777</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5104,6 +5304,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092455</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5209,6 +5414,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092482</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5314,6 +5524,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092566</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5419,8 +5634,58 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112092449</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>